--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -8755,20 +8755,56 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="11"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>DEMO-REJECTED</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Deliberately rejected trades (demo): OT-X is other risks under BCBS, A11 has matured</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="E21" s="20"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="I21" s="21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="21">
+        <v>0</v>
+      </c>
+      <c r="L21" s="21">
+        <v>0</v>
+      </c>
       <c r="M21" s="22"/>
-      <c r="N21" s="11"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="11"/>
@@ -14045,8 +14081,10 @@
       <c r="A43" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>273</v>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>DEMO-REJECTED</t>
+        </is>
       </c>
       <c r="C43" s="11" t="s">
         <v>241</v>
@@ -14707,8 +14745,10 @@
       <c r="A55" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>304</v>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>DEMO-REJECTED</t>
+        </is>
       </c>
       <c r="C55" s="11" t="s">
         <v>45</v>
@@ -23374,7 +23414,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="8" customWidth="1"/>
@@ -23404,6 +23444,7 @@
     <col min="25" max="25" width="15.7109375" style="27" customWidth="1"/>
     <col min="26" max="26" width="15.7109375" style="27" customWidth="1"/>
     <col min="27" max="27" width="11.7109375" style="28" customWidth="1"/>
+    <col min="28" max="28" width="34.7109375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="34" customHeight="1">
@@ -23416,7 +23457,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="42" customHeight="1">
+    <row r="4" spans="1:28" ht="42" customHeight="1">
       <c r="A4" s="31" t="s">
         <v>259</v>
       </c>
@@ -23497,6 +23538,11 @@
       </c>
       <c r="AA4" s="31" t="s">
         <v>508</v>
+      </c>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:27">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -42,6 +42,7 @@
     <definedName name="MultiplierFloor">Params!$C$8</definedName>
     <definedName name="Regime">Params!$C$22</definedName>
     <definedName name="ReportingCcy">Params!$C$6</definedName>
+    <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$C$12</definedName>
     <definedName name="SF_Table">Params!$A$27:$I$53</definedName>
     <definedName name="VolatilityFactor">Params!$C$17</definedName>
@@ -23459,6 +23460,12 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="30" t="str">
+        <f>ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$N,Trades!$A:$W,Params!$A:$H)</f>
+        <v>No results: press Run SA-CCR.</v>
+      </c>
+    </row>
     <row r="4" spans="1:28" ht="42" customHeight="1">
       <c r="A4" s="31" t="s">
         <v>259</v>
@@ -23942,6 +23949,11 @@
       <c r="AA20" s="36"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="OUT OF DATE">
+      <formula>LEFT(A3,LEN("OUT OF DATE"))="OUT OF DATE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -392,7 +392,7 @@
     <t>Modules</t>
   </si>
   <si>
-    <t>M_Main (macros), M_Engine (calculation), M_Formulas (public SACCR_* functions), M_Config (layout constants), M_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction - runs on Windows and Mac, 32 and 64 bit.</t>
+    <t>M_Main (macros), CORE_Engine (calculation), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction - runs on Windows and Mac, 32 and 64 bit.</t>
   </si>
   <si>
     <t>Parameters</t>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -49,6 +49,28 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23461,8 +23483,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="str">
-        <f>ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$N,Trades!$A:$W,Params!$A:$H)</f>
+      <c r="A3" s="30" t="str" cm="1">
+        <f t="array" ref="A3">ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$N,Trades!$A:$W,Params!$A:$H)</f>
         <v>No results: press Run SA-CCR.</v>
       </c>
     </row>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -3009,101 +3009,175 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="55">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="175" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -42,12 +42,35 @@
     <definedName name="MultiplierFloor">Params!$C$8</definedName>
     <definedName name="Regime">Params!$C$22</definedName>
     <definedName name="ReportingCcy">Params!$C$6</definedName>
+    <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$C$12</definedName>
     <definedName name="SF_Table">Params!$A$27:$I$53</definedName>
     <definedName name="VolatilityFactor">Params!$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2986,101 +3009,175 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="55">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="175" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23459,6 +23556,12 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="30" t="str" cm="1">
+        <f t="array" ref="A3">ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$N,Trades!$A:$W,Params!$A:$H)</f>
+        <v>No results: press Run SA-CCR.</v>
+      </c>
+    </row>
     <row r="4" spans="1:28" ht="42" customHeight="1">
       <c r="A4" s="31" t="s">
         <v>259</v>
@@ -23942,6 +24045,11 @@
       <c r="AA20" s="36"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="OUT OF DATE">
+      <formula>LEFT(A3,LEN("OUT OF DATE"))="OUT OF DATE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="917">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2783,6 +2783,48 @@
   </si>
   <si>
     <t>Collateral is an input after haircuts.</t>
+  </si>
+  <si>
+    <t>IR: currency (hedging set); inflation as the currency followed by -INFL, e.g. EUR-INFL, in its own hedging set [Art. 277(4)(a), 277a(1)]. FX: currency pair, e.g. EUR/USD (order is normalised and the sign adjusted). CR / EQ: reference entity or index name. CO: commodity type (trades with the same text are netted as one type). OT (CRR other risks): primary risk driver.</t>
+  </si>
+  <si>
+    <t>Hedging set per currency; buckets &lt;1y, 1-5y, &gt;5y on E; EN = sqrt(D1^2+D2^2+D3^2+1.4D1D2+1.4D2D3+0.6D1D3); AddOn = 0.5% x EN [CRE52.57, Art. 280a]. BCBS only: IRBucketOffset = FALSE uses the sum of absolute bucket values [CRE52.57(5)]; a CRR netting set with IR trades is then INVALID.</t>
+  </si>
+  <si>
+    <t>Simplified SA-CCR and OEM (CRR Art. 281-282), CCP exposures, SFTs, CVA and RWA; collateral haircuts (enter C after haircuts); several margin agreements in one netting set, or one agreement over several netting sets; automatic risk-driver mapping (RTS 2021/931). The optional reductions for sold options and sold credit protection (Art. 274(5), (7)) are not applied, which gives a higher EAD.</t>
+  </si>
+  <si>
+    <t>CRR climatic conditions: 18%, the factor of every commodity hedging set except electricity [Art. 277a(1)(e)(v), 280e(5)]. Unrated single names: enter CQS3 (0.54%), CQS5 (1.6%) where Art. 128 applies, or the step mapped from an internal rating [Art. 280c(5)(a)].</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CRE52.57(5); CRR allows TRUE only (Art. 280a(3))</t>
+  </si>
+  <si>
+    <t>CRR Art. 277(4)(b), 277a(1)(e)(v), 280e(5)</t>
+  </si>
+  <si>
+    <t>VERIFIED: 18% [Art. 280e(5)]</t>
+  </si>
+  <si>
+    <t>VERIFIED (CRR Art. 277(4)(a), 277a(1))</t>
+  </si>
+  <si>
+    <t>Sub-classes CQS1-CQS6 added. Unrated: enter CQS3 (0.54%), CQS5 (1.6%) where Art. 128 applies, or the step mapped from an internal rating [Art. 280c(5)(a)].</t>
+  </si>
+  <si>
+    <t>Art. 280a(3): the bucket formula only; no sum of absolute bucket values.</t>
+  </si>
+  <si>
+    <t>CRR netting sets cannot use the sum of absolutes</t>
+  </si>
+  <si>
+    <t>Common core. IRBucketOffset = FALSE applies to BCBS only; a CRR netting set with IR trades is then INVALID.</t>
+  </si>
+  <si>
+    <t>Optional reductions not applied: sold options and sold protection are calculated as ordinary trades, which gives a higher EAD (permitted).</t>
   </si>
 </sst>
 </file>
@@ -3605,7 +3647,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>23</v>
+        <v>903</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="28" customHeight="1">
@@ -3699,7 +3741,7 @@
         <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>46</v>
+        <v>904</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -3925,15 +3967,15 @@
         <v>99</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>100</v>
+        <v>905</v>
       </c>
     </row>
     <row r="63" spans="2:3" ht="28" customHeight="1">
       <c r="B63" s="4" t="s">
-        <v>101</v>
+        <v>907</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>102</v>
+        <v>906</v>
       </c>
     </row>
     <row r="64" spans="2:3">
@@ -6561,7 +6603,7 @@
         <v>743</v>
       </c>
       <c r="I14" s="54" t="s">
-        <v>822</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1">
@@ -6590,7 +6632,7 @@
         <v>769</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>829</v>
+        <v>911</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39" customHeight="1">
@@ -6671,13 +6713,13 @@
         <v>847</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>848</v>
+        <v>912</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>748</v>
       </c>
       <c r="I18" s="54" t="s">
-        <v>849</v>
+        <v>770</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1">
@@ -6778,22 +6820,22 @@
         <v>863</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>864</v>
+        <v>913</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>775</v>
+        <v>914</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>865</v>
+        <v>915</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>660</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>866</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1">
@@ -6845,7 +6887,7 @@
         <v>875</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>876</v>
+        <v>916</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>769</v>
@@ -7283,7 +7325,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>164</v>
+        <v>908</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -8041,7 +8083,7 @@
         <v>167</v>
       </c>
       <c r="I52" s="18" t="s">
-        <v>240</v>
+        <v>909</v>
       </c>
     </row>
     <row r="53" spans="1:9">
